--- a/branches/feature-careteam/StructureDefinition-RIVManagingTeam-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-RIVManagingTeam-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:06:47+00:00</t>
+    <t>2026-09-21T07:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -885,7 +885,7 @@
 ctm-2</t>
   </si>
   <si>
-    <t>Personal.id,Personal.namn,Personal.befattning</t>
+    <t>Personal</t>
   </si>
   <si>
     <t>FiveWs.actor</t>

--- a/branches/feature-careteam/StructureDefinition-RIVManagingTeam-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-RIVManagingTeam-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:30:27+00:00</t>
+    <t>2026-09-21T07:49:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-RIVManagingTeam-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-RIVManagingTeam-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:49:30+00:00</t>
+    <t>2026-09-21T07:54:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-RIVManagingTeam-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-RIVManagingTeam-careteam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:54:52+00:00</t>
+    <t>2026-09-21T08:04:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-RIVManagingTeam-careteam.xlsx
+++ b/branches/feature-careteam/StructureDefinition-RIVManagingTeam-careteam.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2589" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T08:04:47+00:00</t>
+    <t>2026-10-14T09:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,10 +265,7 @@
 </t>
   </si>
   <si>
-    <t>Planned participants in the coordination and delivery of care</t>
-  </si>
-  <si>
-    <t>The Care Team includes all the people and organizations who plan to participate in the coordination and delivery of care.</t>
+    <t>Ett vård- eller omsorgsteam vid en vårdande enhet eller omsorgsenhet. Teamet kan vara organiserat kring en invånare, ha egna kontaktvägar och utgöra kontaktväg för en fast kontakt.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -297,10 +294,10 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+    <t>Resursens logiska id</t>
+  </si>
+  <si>
+    <t>Logiskt id som tilldelas av den server som lagrar resursen. Id:t ändras inte under resursens livstid.</t>
   </si>
   <si>
     <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
@@ -316,10 +313,10 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>Metadata om resursen</t>
+  </si>
+  <si>
+    <t>Metadata som hanteras av infrastrukturen, till exempel versions-id och tidpunkt för senaste ändring.</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -336,10 +333,10 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+    <t>Regler som innehållet skapats enligt</t>
+  </si>
+  <si>
+    <t>Referens till regler som följdes när resursen skapades och som mottagaren måste känna till för att tolka innehållet. Förväntas inte användas.</t>
   </si>
   <si>
     <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
@@ -355,10 +352,10 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
+    <t>Språk för resursens innehåll</t>
+  </si>
+  <si>
+    <t>Det språk som resursens textinnehåll är skrivet på.</t>
   </si>
   <si>
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
@@ -387,10 +384,10 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+    <t>Läsbar sammanfattning</t>
+  </si>
+  <si>
+    <t>Sammanfattning av resursens innehåll i läsbar form, avsedd för visning för människor.</t>
   </si>
   <si>
     <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
@@ -417,10 +414,10 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+    <t>Inbäddade resurser</t>
+  </si>
+  <si>
+    <t>Resurser som ingår i denna resurs och saknar egen identitet utanför den. Bör undvikas när de refererade resurserna kan hämtas separat.</t>
   </si>
   <si>
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
@@ -439,21 +436,14 @@
     <t>CareTeam.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>Tillägg</t>
+  </si>
+  <si>
+    <t>Ytterligare information som inte ingår i basresursen, uttryckt med extensioner.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -466,14 +456,10 @@
     <t>CareTeam.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
+    <t>Tillägg som ändrar tolkningen</t>
+  </si>
+  <si>
+    <t>Extensioner som ändrar betydelsen av resursen eller av element i den. Mottagaren får inte ignorera dem. Förväntas inte användas.</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -486,10 +472,10 @@
 </t>
   </si>
   <si>
-    <t>Identifierare för team</t>
-  </si>
-  <si>
-    <t>Identifierare som kan användas för att identifiera teamet.</t>
+    <t>Teamets id</t>
+  </si>
+  <si>
+    <t>Unik identifierare för teamet.</t>
   </si>
   <si>
     <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R5/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
@@ -513,13 +499,13 @@
     <t>proposed | active | suspended | inactive | entered-in-error</t>
   </si>
   <si>
-    <t>Indicates the current state of the care team.</t>
+    <t>Anger teamets status: active betyder att teamet är aktuellt, inactive att det har upphört, suspended att det tillfälligt inte är aktuellt, proposed att det är föreslaget men inte fastställt och entered-in-error att resursen har registrerats felaktigt och inte ska användas.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains the code entered-in-error that marks the care team as not currently valid.</t>
   </si>
   <si>
-    <t>Indicates the status of the care team.</t>
+    <t>Status för teamet.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/care-team-status|5.0.0</t>
@@ -538,10 +524,10 @@
 </t>
   </si>
   <si>
-    <t>Kategori av CareTeam</t>
-  </si>
-  <si>
-    <t>Anger att resursen avser ett team.</t>
+    <t>Kategori: team</t>
+  </si>
+  <si>
+    <t>Anger att resursen beskriver ett team och skiljer den från andra användningar av CareTeam, till exempel fast kontakt. Värdet är fast och är alltid koden team.</t>
   </si>
   <si>
     <t>There may be multiple axis of categorization and one team may serve multiple purposes.</t>
@@ -561,10 +547,10 @@
     <t>example</t>
   </si>
   <si>
-    <t>Indicates the type of care team.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-team-category|5.0.0</t>
+    <t>Kategori av CareTeam.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/care-team-category</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -592,7 +578,17 @@
     <t>CareTeam.category.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -615,10 +611,10 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
+    <t>Kod som anger kategori</t>
+  </si>
+  <si>
+    <t>Kodad kategori från kodsystemet Typ av CareTeam. Värdet är fast.</t>
   </si>
   <si>
     <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
@@ -636,17 +632,142 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>CareTeam.category.text</t>
+    <t>CareTeam.category.coding.id</t>
+  </si>
+  <si>
+    <t>CareTeam.category.coding.extension</t>
+  </si>
+  <si>
+    <t>CareTeam.category.coding.system</t>
+  </si>
+  <si>
+    <t>Kodsystem</t>
+  </si>
+  <si>
+    <t>Identifierar det kodsystem som koden kommer från.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should be an absolute reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>CareTeam.category.coding.version</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+    <t>Version av kodsystemet</t>
+  </si>
+  <si>
+    <t>Version av kodsystemet, om det är relevant.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>CareTeam.category.coding.code</t>
+  </si>
+  <si>
+    <t>Kod</t>
+  </si>
+  <si>
+    <t>Koden för kategorin.</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cod-1
+</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>CareTeam.category.coding.display</t>
+  </si>
+  <si>
+    <t>Klartext för koden</t>
+  </si>
+  <si>
+    <t>Kodens benämning i klartext, avsedd för visning.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CareTeam.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Vald direkt av användare</t>
+  </si>
+  <si>
+    <t>Anger om koden valts direkt av en användare. Förväntas inte användas.</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CareTeam.category.text</t>
+  </si>
+  <si>
+    <t>Kategorin i klartext</t>
+  </si>
+  <si>
+    <t>Kategorin uttryckt i klartext.</t>
   </si>
   <si>
     <t>Very often the text is the same as a displayName of one of the codings.</t>
@@ -670,7 +791,7 @@
     <t>Teamets namn</t>
   </si>
   <si>
-    <t>Namn på det vård- eller omsorgsteam som beskrivs.</t>
+    <t>Teamets namn i den form det ska visas för invånaren.</t>
   </si>
   <si>
     <t>The meaning/purpose of the team is conveyed in CareTeam.category.  This element may also convey semantics of the team (e.g. "Red trauma team"), but its primary purpose is to distinguish between identical teams in a human-friendly way.  ("Team 18735" isn't as friendly.).</t>
@@ -693,10 +814,10 @@
 </t>
   </si>
   <si>
-    <t>Invånare som teamet gäller för</t>
-  </si>
-  <si>
-    <t>Invånare som teamet gäller för. Kan utelämnas om teamet inte är direkt kopplat till en specifik invånare.</t>
+    <t>Invånare</t>
+  </si>
+  <si>
+    <t>Den invånare som teamet är organiserat kring. Utelämnas om teamet inte är kopplat till en specifik invånare.</t>
   </si>
   <si>
     <t>Use Group for care provision to all members of the group (e.g. group therapy).  Use Patient for care provision to an individual patient.</t>
@@ -719,10 +840,10 @@
 </t>
   </si>
   <si>
-    <t>Time period team covers</t>
-  </si>
-  <si>
-    <t>Indicates when the team did (or is intended to) come into effect and end.</t>
+    <t>Giltighetsperiod</t>
+  </si>
+  <si>
+    <t>Den period under vilken teamet gäller. Om subject är angivet avser perioden teamets koppling till invånaren, annars teamets giltighet i allmänhet.</t>
   </si>
   <si>
     <t>Allows tracking what team(s) are in effect at a particular time.</t>
@@ -747,7 +868,7 @@
     <t>Startdatum</t>
   </si>
   <si>
-    <t>Det datum då teamet börjar gälla i det aktuella sammanhanget.</t>
+    <t>Datum då teamet börjar gälla.</t>
   </si>
   <si>
     <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
@@ -772,7 +893,7 @@
     <t>Slutdatum</t>
   </si>
   <si>
-    <t>Det datum då teamet upphör att gälla i det aktuella sammanhanget.</t>
+    <t>Datum då teamet upphör att gälla. Saknas slutdatum gäller teamet tills vidare.</t>
   </si>
   <si>
     <t>The end value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
@@ -800,7 +921,7 @@
     <t>Deltagare i teamet</t>
   </si>
   <si>
-    <t>Aktörer som ingår i eller representerar teamet. Deltagare kan exempelvis vara vård- och omsorgspersonal, roll/funktion eller annan relevant aktör.</t>
+    <t>Vård- eller omsorgspersonal som ingår i teamet.</t>
   </si>
   <si>
     <t>ctm-1:CareTeam.participant.onBehalfOf can only be populated when CareTeam.participant.member is a Practitioner {onBehalfOf.exists() implies (member.resolve() is Practitioner)}
@@ -833,16 +954,19 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
     <t>CareTeam.participant.role</t>
   </si>
   <si>
-    <t>Type of involvement</t>
-  </si>
-  <si>
-    <t>Indicates specific responsibility of an individual within the care team, such as "Primary care physician", "Trained social worker counselor", "Caregiver", etc.</t>
+    <t>Deltagarens roll i teamet</t>
+  </si>
+  <si>
+    <t>Den roll eller funktion som deltagaren har i teamet.</t>
   </si>
   <si>
     <t>Roles may sometimes be inferred by type of Practitioner.  These are relationships that hold only within the context of the care team.  General relationships should be handled as properties of the Patient resource directly.  If a participant has multiple roles within the team, then there should be multiple participants.</t>
@@ -874,7 +998,7 @@
     <t>Teamdeltagare</t>
   </si>
   <si>
-    <t>Aktör som ingår i teamet, exempelvis en person i roll eller en person.</t>
+    <t>Den person som ingår i teamet, uttryckt antingen som personen i sin roll vid en enhet (PractitionerRole) eller som person (Practitioner).</t>
   </si>
   <si>
     <t>Patient only needs to be listed if they have a role other than "subject of care".
@@ -904,10 +1028,10 @@
 </t>
   </si>
   <si>
-    <t>Organization of the practitioner</t>
-  </si>
-  <si>
-    <t>The organization of the practitioner.</t>
+    <t>Organisation som deltagaren företräder</t>
+  </si>
+  <si>
+    <t>Organisation som deltagaren företräder i teamet. Förväntas normalt inte användas.</t>
   </si>
   <si>
     <t>Practitioners can be associated with multiple organizations.  This element indicates which organization they were acting on behalf of.</t>
@@ -924,10 +1048,10 @@
 Timing</t>
   </si>
   <si>
-    <t>When the member is generally available within this care team</t>
-  </si>
-  <si>
-    <t>When the member is generally available within this care team.</t>
+    <t>Deltagarens tillgänglighet</t>
+  </si>
+  <si>
+    <t>Period eller schema då deltagaren ingår i teamet. Förväntas normalt inte användas.</t>
   </si>
   <si>
     <t>This is populated while creating / managing the CareTeam to ensure there is coverage when servicing CarePlan activities from the Schedule.</t>
@@ -943,10 +1067,10 @@
 </t>
   </si>
   <si>
-    <t>Why the care team exists</t>
-  </si>
-  <si>
-    <t>Describes why the care team exists.</t>
+    <t>Anledning</t>
+  </si>
+  <si>
+    <t>Används inte för team.</t>
   </si>
   <si>
     <t>Indicates the reason for the care team.</t>
@@ -961,10 +1085,10 @@
     <t>CareTeam.managingOrganization</t>
   </si>
   <si>
-    <t>Organization responsible for the care team</t>
-  </si>
-  <si>
-    <t>The organization responsible for the care team.</t>
+    <t>Enhet som teamet tillhör</t>
+  </si>
+  <si>
+    <t>Den vårdande enhet eller omsorgsenhet som teamet tillhör.</t>
   </si>
   <si>
     <t>Allows for multiple organizations to collaboratively manage cross-organizational, longitudinal care plan.</t>
@@ -977,10 +1101,10 @@
 </t>
   </si>
   <si>
-    <t>Kontaktuppgifter till teamet</t>
-  </si>
-  <si>
-    <t>Kontaktuppgifter som ska användas av invånaren för att nå teamet. Kontaktuppgifterna kan även användas när en fast kontakt nås via detta team.</t>
+    <t>Kontaktväg till teamet</t>
+  </si>
+  <si>
+    <t>Kontaktväg som invånaren använder för att nå teamet, till exempel ett telefonnummer eller en webbadress. Kontaktvägen används även när en fast kontakt nås via teamet.</t>
   </si>
   <si>
     <t>The ContactPoint.use code of home is not appropriate to use. These contacts are not the contact details of individual care team members.</t>
@@ -1002,10 +1126,10 @@
 </t>
   </si>
   <si>
-    <t>Tillgänglighet för kontaktväg</t>
-  </si>
-  <si>
-    <t>Anger under vilka tider och veckodagar kontaktvägen är tillgänglig.</t>
+    <t>Kontakttider</t>
+  </si>
+  <si>
+    <t>Anger veckodagar och tider då kontaktvägen är tillgänglig, till exempel telefontider.</t>
   </si>
   <si>
     <t>CareTeam.telecom.extension:availability.id</t>
@@ -1153,10 +1277,6 @@
     <t>CareTeam.telecom.extension.value[x].availableTime.allDay</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
     <t>Always available? i.e. 24 hour service</t>
   </si>
   <si>
@@ -1295,10 +1415,10 @@
     <t>CareTeam.telecom.system</t>
   </si>
   <si>
-    <t>phone | fax | email | pager | url | sms | other</t>
-  </si>
-  <si>
-    <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
+    <t>Typ av kontaktväg</t>
+  </si>
+  <si>
+    <t>Anger vilken sorts kontaktväg det är, till exempel telefon, e-post eller webbadress.</t>
   </si>
   <si>
     <t>Telecommunications form for contact point.</t>
@@ -1326,10 +1446,10 @@
     <t>CareTeam.telecom.value</t>
   </si>
   <si>
-    <t>The actual contact point details</t>
-  </si>
-  <si>
-    <t>The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
+    <t>Kontaktuppgift</t>
+  </si>
+  <si>
+    <t>Själva kontaktuppgiften, till exempel ett telefonnummer eller en webbadress, i den form den ska visas för invånaren.</t>
   </si>
   <si>
     <t>Additional text data such as phone extension numbers, or notes about use of the contact are sometimes included in the value.</t>
@@ -1353,10 +1473,10 @@
     <t>CareTeam.telecom.use</t>
   </si>
   <si>
-    <t>home | work | temp | old | mobile - purpose of this contact point</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for the contact point.</t>
+    <t>Avsedd användning</t>
+  </si>
+  <si>
+    <t>Anger avsedd användning av kontaktvägen.</t>
   </si>
   <si>
     <t>Applications can assume that a contact is current unless it explicitly says that it is temporary or old.</t>
@@ -1387,10 +1507,10 @@
 </t>
   </si>
   <si>
-    <t>Specify preferred order of use (1 = highest)</t>
-  </si>
-  <si>
-    <t>Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
+    <t>Prioritetsordning</t>
+  </si>
+  <si>
+    <t>Ordning i vilken kontaktvägarna bör användas. Värdet 1 anger högst prioritet.</t>
   </si>
   <si>
     <t>Note that rank does not necessarily follow the order in which the contacts are represented in the instance.
@@ -1404,10 +1524,10 @@
     <t>CareTeam.telecom.period</t>
   </si>
   <si>
-    <t>Time period when the contact point was/is in use</t>
-  </si>
-  <si>
-    <t>Time period when the contact point was/is in use.</t>
+    <t>Giltighetsperiod för kontaktvägen</t>
+  </si>
+  <si>
+    <t>Period under vilken kontaktvägen gäller.</t>
   </si>
   <si>
     <t>ContactPoint.period</t>
@@ -1426,7 +1546,7 @@
     <t>Kommentar</t>
   </si>
   <si>
-    <t>Kommentar eller kompletterande information om teamet.</t>
+    <t>Kommentar i fritext om teamet, till exempel vägledning om när och hur invånaren kan ta kontakt.</t>
   </si>
   <si>
     <t>Team.kommentar</t>
@@ -1746,7 +1866,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO62"/>
+  <dimension ref="A1:AO69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.8671875" customWidth="true" bestFit="true"/>
@@ -1947,10 +2067,10 @@
         <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="M2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="M2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -2013,19 +2133,19 @@
         <v>78</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AK2" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AM2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>78</v>
@@ -2033,10 +2153,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2047,28 +2167,28 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2118,13 +2238,13 @@
         <v>78</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>78</v>
@@ -2150,10 +2270,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2164,25 +2284,25 @@
         <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2233,19 +2353,19 @@
         <v>78</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>78</v>
@@ -2265,10 +2385,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2279,28 +2399,28 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2350,19 +2470,19 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>78</v>
@@ -2382,10 +2502,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2396,7 +2516,7 @@
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>78</v>
@@ -2408,16 +2528,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2443,43 +2563,43 @@
         <v>78</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
@@ -2499,21 +2619,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>78</v>
@@ -2525,16 +2645,16 @@
         <v>78</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2584,28 +2704,28 @@
         <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="AG7" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI7" t="s" s="2">
+      <c r="AJ7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>78</v>
@@ -2616,14 +2736,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2642,16 +2762,16 @@
         <v>78</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2701,7 +2821,7 @@
         <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -2710,19 +2830,19 @@
         <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>78</v>
@@ -2733,14 +2853,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2759,17 +2879,15 @@
         <v>78</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>78</v>
@@ -2818,7 +2936,7 @@
         <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2830,7 +2948,7 @@
         <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -2839,7 +2957,7 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2850,14 +2968,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2870,26 +2988,22 @@
         <v>78</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
       </c>
@@ -2937,7 +3051,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2949,7 +3063,7 @@
         <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -2958,7 +3072,7 @@
         <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>78</v>
@@ -2969,10 +3083,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2986,28 +3100,28 @@
         <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>78</v>
@@ -3056,7 +3170,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3068,19 +3182,19 @@
         <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>78</v>
@@ -3088,10 +3202,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3102,28 +3216,28 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I12" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3149,13 +3263,13 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -3173,31 +3287,31 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>78</v>
@@ -3205,10 +3319,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3216,34 +3330,34 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H13" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G13" t="s" s="2">
+      <c r="I13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H13" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>78</v>
@@ -3253,7 +3367,7 @@
         <v>78</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>78</v>
@@ -3268,13 +3382,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3292,7 +3406,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3304,13 +3418,13 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -3324,10 +3438,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3338,7 +3452,7 @@
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
@@ -3350,13 +3464,13 @@
         <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3407,16 +3521,16 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>78</v>
@@ -3428,7 +3542,7 @@
         <v>78</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
@@ -3439,14 +3553,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3465,16 +3579,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3512,19 +3626,19 @@
         <v>78</v>
       </c>
       <c r="AB15" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AC15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AC15" t="s" s="2">
+      <c r="AD15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AD15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE15" t="s" s="2">
+      <c r="AF15" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3536,7 +3650,7 @@
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
@@ -3545,7 +3659,7 @@
         <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3556,10 +3670,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3567,34 +3681,34 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -3643,7 +3757,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3655,7 +3769,7 @@
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -3664,21 +3778,21 @@
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>196</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3689,7 +3803,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
@@ -3698,23 +3812,19 @@
         <v>78</v>
       </c>
       <c r="J17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="K17" t="s" s="2">
-        <v>198</v>
-      </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>78</v>
       </c>
@@ -3762,19 +3872,19 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -3783,53 +3893,53 @@
         <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3867,89 +3977,89 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>78</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>102</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -3998,42 +4108,42 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4044,30 +4154,30 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -4115,42 +4225,42 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4161,28 +4271,30 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>178</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
       </c>
@@ -4230,19 +4342,19 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
@@ -4251,32 +4363,32 @@
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>78</v>
@@ -4285,21 +4397,21 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4335,31 +4447,31 @@
         <v>78</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>78</v>
@@ -4368,16 +4480,16 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>78</v>
+        <v>228</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>229</v>
       </c>
@@ -4393,16 +4505,16 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>230</v>
@@ -4416,7 +4528,9 @@
       <c r="N23" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4464,19 +4578,19 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>78</v>
@@ -4494,7 +4608,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>238</v>
       </c>
@@ -4510,19 +4624,19 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>239</v>
@@ -4533,13 +4647,13 @@
       <c r="N24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="O24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q24" t="s" s="2">
-        <v>242</v>
-      </c>
+      <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
         <v>78</v>
       </c>
@@ -4589,13 +4703,13 @@
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
@@ -4629,27 +4743,29 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4704,68 +4820,72 @@
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AK25" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AL25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AO25" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>252</v>
       </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>253</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>78</v>
+        <v>253</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H26" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>198</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>177</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4813,28 +4933,28 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>179</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -4843,46 +4963,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>138</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -4930,28 +5050,28 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>187</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4962,46 +5082,42 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>256</v>
+        <v>78</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="J28" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>137</v>
-      </c>
       <c r="L28" t="s" s="2">
-        <v>257</v>
+        <v>173</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5049,19 +5165,19 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
@@ -5070,7 +5186,7 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5081,21 +5197,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>78</v>
@@ -5104,19 +5220,19 @@
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>181</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>182</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5142,43 +5258,43 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>264</v>
+        <v>78</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>265</v>
+        <v>78</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>186</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>266</v>
+        <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
@@ -5187,13 +5303,13 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>267</v>
+        <v>177</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>268</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
@@ -5212,16 +5328,16 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H30" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H30" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="I30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>270</v>
@@ -5283,42 +5399,42 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO30" t="s" s="2">
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
         <v>278</v>
       </c>
-    </row>
-    <row r="31" hidden="true">
-      <c r="A31" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5329,113 +5445,115 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H31" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H31" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q31" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
+      <c r="R31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="P31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AJ31" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>78</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5446,11 +5564,11 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H32" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5458,20 +5576,16 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N32" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="O32" t="s" s="2">
-        <v>290</v>
-      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5519,19 +5633,19 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
@@ -5540,21 +5654,21 @@
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>291</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>78</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5565,7 +5679,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
@@ -5577,13 +5691,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>292</v>
+        <v>207</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>293</v>
+        <v>173</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>294</v>
+        <v>174</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5610,13 +5724,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>295</v>
+        <v>78</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5634,28 +5748,28 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -5666,14 +5780,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5689,21 +5803,21 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>180</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5751,7 +5865,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5763,7 +5877,7 @@
         <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -5772,7 +5886,7 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5781,16 +5895,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5800,27 +5914,29 @@
         <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>303</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
@@ -5868,7 +5984,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5880,7 +5996,7 @@
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
@@ -5889,7 +6005,7 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -5900,10 +6016,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5914,27 +6030,29 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>177</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -5959,13 +6077,13 @@
         <v>78</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>78</v>
+        <v>306</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -5983,19 +6101,19 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>179</v>
+        <v>301</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>180</v>
+        <v>307</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -6004,53 +6122,53 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>181</v>
+        <v>308</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>78</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>137</v>
+        <v>311</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>138</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>183</v>
+        <v>313</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>140</v>
+        <v>314</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6088,58 +6206,56 @@
         <v>78</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>187</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>78</v>
+        <v>315</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>78</v>
+        <v>316</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>78</v>
+        <v>317</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>181</v>
+        <v>318</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>78</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>78</v>
       </c>
@@ -6148,28 +6264,30 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H38" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
       </c>
@@ -6217,19 +6335,19 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>187</v>
+        <v>320</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>325</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>78</v>
@@ -6249,10 +6367,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6263,7 +6381,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6275,16 +6393,20 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>91</v>
+        <v>327</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>177</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6332,19 +6454,19 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>179</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
@@ -6353,7 +6475,7 @@
         <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6364,10 +6486,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6378,7 +6500,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -6390,13 +6512,13 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6423,31 +6545,31 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>78</v>
+        <v>336</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>187</v>
+        <v>332</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6459,13 +6581,13 @@
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6479,10 +6601,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6490,39 +6612,39 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G41" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K41" t="s" s="2">
-        <v>103</v>
+        <v>321</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>78</v>
@@ -6564,19 +6686,19 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
@@ -6585,7 +6707,7 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6596,10 +6718,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6607,14 +6729,14 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H42" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6622,15 +6744,17 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6679,19 +6803,19 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>333</v>
+        <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
@@ -6700,7 +6824,7 @@
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -6711,10 +6835,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6725,7 +6849,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -6737,13 +6861,13 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6794,16 +6918,16 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>78</v>
@@ -6815,7 +6939,7 @@
         <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6826,14 +6950,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6852,16 +6976,16 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6899,19 +7023,19 @@
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AC44" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AC44" t="s" s="2">
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AD44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE44" t="s" s="2">
+      <c r="AF44" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6923,7 +7047,7 @@
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
@@ -6932,7 +7056,7 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -6943,44 +7067,44 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H45" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="I45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>343</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7028,7 +7152,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>344</v>
+        <v>186</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7040,7 +7164,7 @@
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>345</v>
+        <v>139</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
@@ -7060,10 +7184,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7074,7 +7198,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>78</v>
@@ -7086,13 +7210,13 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>198</v>
+        <v>90</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7143,16 +7267,16 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>78</v>
@@ -7164,7 +7288,7 @@
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7175,21 +7299,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -7201,17 +7325,15 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>138</v>
+        <v>359</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7248,19 +7370,19 @@
         <v>78</v>
       </c>
       <c r="AB47" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AC47" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AC47" t="s" s="2">
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AD47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE47" t="s" s="2">
+      <c r="AF47" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7272,7 +7394,7 @@
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
@@ -7281,7 +7403,7 @@
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7290,12 +7412,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7303,39 +7425,39 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>78</v>
+        <v>366</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>78</v>
@@ -7353,13 +7475,13 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>355</v>
+        <v>78</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>356</v>
+        <v>78</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7377,28 +7499,28 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>358</v>
+        <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7407,12 +7529,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7420,33 +7542,31 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H49" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H49" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7494,19 +7614,19 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
@@ -7515,7 +7635,7 @@
         <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7524,12 +7644,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7540,32 +7660,28 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K50" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>369</v>
-      </c>
       <c r="L50" t="s" s="2">
-        <v>370</v>
+        <v>173</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7613,28 +7729,28 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>374</v>
+        <v>175</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>366</v>
+        <v>176</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7643,48 +7759,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>369</v>
+        <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>378</v>
+        <v>180</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>379</v>
+        <v>181</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7720,40 +7834,40 @@
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>381</v>
+        <v>186</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>382</v>
+        <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7762,12 +7876,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7775,32 +7889,32 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7849,7 +7963,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7861,7 +7975,7 @@
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>386</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -7881,10 +7995,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7895,7 +8009,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
@@ -7907,13 +8021,13 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7964,16 +8078,16 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>78</v>
@@ -7985,7 +8099,7 @@
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -7996,14 +8110,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8022,16 +8136,16 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8069,19 +8183,19 @@
         <v>78</v>
       </c>
       <c r="AB54" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AC54" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AC54" t="s" s="2">
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AD54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE54" t="s" s="2">
+      <c r="AF54" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8093,7 +8207,7 @@
         <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
@@ -8102,7 +8216,7 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8111,12 +8225,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8124,34 +8238,32 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H55" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H55" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>198</v>
+        <v>108</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8176,13 +8288,13 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>78</v>
+        <v>396</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>78</v>
+        <v>397</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8200,22 +8312,22 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK55" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
@@ -8246,19 +8358,19 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K56" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>402</v>
@@ -8323,13 +8435,13 @@
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>78</v>
+        <v>406</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
@@ -8349,10 +8461,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8363,28 +8475,32 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H57" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>109</v>
+        <v>409</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8408,13 +8524,13 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8432,34 +8548,34 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>414</v>
+        <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58">
@@ -8467,7 +8583,7 @@
         <v>416</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8478,28 +8594,28 @@
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H58" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H58" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>198</v>
+        <v>409</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>420</v>
@@ -8557,13 +8673,13 @@
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>422</v>
@@ -8572,21 +8688,21 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8597,31 +8713,29 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J59" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="K59" t="s" s="2">
-        <v>109</v>
+        <v>381</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8646,13 +8760,13 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>431</v>
+        <v>78</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8670,19 +8784,19 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -8691,21 +8805,21 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>433</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8716,7 +8830,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8725,20 +8839,18 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>436</v>
+        <v>207</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>437</v>
+        <v>173</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8787,19 +8899,19 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>440</v>
+        <v>175</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -8808,32 +8920,32 @@
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -8842,18 +8954,20 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>222</v>
+        <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>442</v>
+        <v>180</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -8890,31 +9004,31 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>444</v>
+        <v>186</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -8923,21 +9037,21 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>445</v>
+        <v>177</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8948,28 +9062,32 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9017,38 +9135,855 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AG62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH62" t="s" s="2">
+      <c r="B64" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G69" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO62" t="s" s="2">
+      <c r="H69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO62">
+  <autoFilter ref="A1:AO69">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9058,7 +9993,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
